--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141069</t>
-  </si>
-  <si>
-    <t>POCI VANL TPS 2X25'S</t>
+    <t>20076772</t>
+  </si>
+  <si>
+    <t>SIMBA CRL CHOCHP 220</t>
   </si>
   <si>
     <t>FES05N</t>
@@ -28,37 +28,22 @@
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141006</t>
-  </si>
-  <si>
-    <t>CAP BTL TEH CLP HJ2S</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20076772</t>
-  </si>
-  <si>
-    <t>SIMBA CRL CHOCHP 220</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20001119</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK 4+2S</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>20141364</t>
@@ -472,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -516,18 +501,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -536,18 +521,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -556,18 +541,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -576,50 +561,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
@@ -28,9 +28,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
@@ -40,7 +37,7 @@
     <t>SOSRO TEH KOTAK 4+2S</t>
   </si>
   <si>
-    <t>4</t>
+    <t>2</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
@@ -52,19 +49,19 @@
     <t>SARIWANGI TWIN 2X30S</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141508</t>
+  </si>
+  <si>
+    <t>KRTINGDAENG BDD3X150</t>
+  </si>
+  <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141508</t>
-  </si>
-  <si>
-    <t>KRTINGDAENG BDD3X150</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -501,18 +498,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -521,18 +518,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -541,18 +538,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -561,10 +558,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20141508</t>
@@ -541,15 +538,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -558,7 +555,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
@@ -41,15 +41,6 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141364</t>
-  </si>
-  <si>
-    <t>SARIWANGI TWIN 2X30S</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>20141508</t>
@@ -451,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -541,26 +532,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,30 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20076772</t>
-  </si>
-  <si>
-    <t>SIMBA CRL CHOCHP 220</t>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
   </si>
   <si>
     <t>FES05N</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20001119</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK 4+2S</t>
   </si>
   <si>
     <t>2</t>
@@ -442,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -486,18 +477,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -506,30 +497,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t/>
   </si>
@@ -433,17 +433,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,8 +463,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -479,11 +486,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -499,7 +506,7 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
@@ -433,18 +433,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,14 +462,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -486,11 +479,11 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -506,7 +499,7 @@
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/FES05N.xlsx
+++ b/E/FES05N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
@@ -28,9 +28,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
@@ -40,7 +37,7 @@
     <t>KRTINGDAENG BDD3X150</t>
   </si>
   <si>
-    <t>7</t>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -477,18 +474,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -497,10 +494,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
